--- a/tests/v1/fixtures/office6m/2026-10/bank_statements/HB_B_USD_2026-09.xlsx
+++ b/tests/v1/fixtures/office6m/2026-10/bank_statements/HB_B_USD_2026-09.xlsx
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>704314.35</v>
+        <v>706464.35</v>
       </c>
       <c r="E2" t="n">
         <v>60508.62</v>
       </c>
       <c r="F2" t="n">
-        <v>764822.97</v>
+        <v>766972.97</v>
       </c>
     </row>
     <row r="3">
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>764822.97</v>
+        <v>766972.97</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>764822.97</v>
+        <v>766972.97</v>
       </c>
     </row>
     <row r="4">
@@ -876,13 +876,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>764822.97</v>
+        <v>766972.97</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>764822.97</v>
+        <v>766972.97</v>
       </c>
     </row>
     <row r="5">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>764822.97</v>
+        <v>766972.97</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>764822.97</v>
+        <v>766972.97</v>
       </c>
     </row>
     <row r="6">
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>764822.97</v>
+        <v>766972.97</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>764822.97</v>
+        <v>766972.97</v>
       </c>
     </row>
     <row r="7">
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>764822.97</v>
+        <v>766972.97</v>
       </c>
       <c r="E7" t="n">
         <v>1150000</v>
       </c>
       <c r="F7" t="n">
-        <v>1914822.97</v>
+        <v>1916972.97</v>
       </c>
     </row>
     <row r="8">
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1914822.97</v>
+        <v>1916972.97</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1914822.97</v>
+        <v>1916972.97</v>
       </c>
     </row>
     <row r="9">
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1914822.97</v>
+        <v>1916972.97</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1914822.97</v>
+        <v>1916972.97</v>
       </c>
     </row>
     <row r="10">
@@ -1032,13 +1032,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1914822.97</v>
+        <v>1916972.97</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1914822.97</v>
+        <v>1916972.97</v>
       </c>
     </row>
     <row r="11">
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1914822.97</v>
+        <v>1916972.97</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1914822.97</v>
+        <v>1916972.97</v>
       </c>
     </row>
     <row r="12">
@@ -1084,13 +1084,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1914822.97</v>
+        <v>1916972.97</v>
       </c>
       <c r="E12" t="n">
         <v>-250000</v>
       </c>
       <c r="F12" t="n">
-        <v>1664822.97</v>
+        <v>1666972.97</v>
       </c>
     </row>
     <row r="13">
@@ -1110,13 +1110,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1664822.97</v>
+        <v>1666972.97</v>
       </c>
       <c r="E13" t="n">
         <v>-300000</v>
       </c>
       <c r="F13" t="n">
-        <v>1364822.97</v>
+        <v>1366972.97</v>
       </c>
     </row>
     <row r="14">
@@ -1136,13 +1136,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1364822.97</v>
+        <v>1366972.97</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1364822.97</v>
+        <v>1366972.97</v>
       </c>
     </row>
     <row r="15">
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1364822.97</v>
+        <v>1366972.97</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1364822.97</v>
+        <v>1366972.97</v>
       </c>
     </row>
     <row r="16">
@@ -1188,13 +1188,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1364822.97</v>
+        <v>1366972.97</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1364822.97</v>
+        <v>1366972.97</v>
       </c>
     </row>
     <row r="17">
@@ -1214,13 +1214,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1364822.97</v>
+        <v>1366972.97</v>
       </c>
       <c r="E17" t="n">
         <v>-600000</v>
       </c>
       <c r="F17" t="n">
-        <v>764822.97</v>
+        <v>766972.97</v>
       </c>
     </row>
     <row r="18">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>764822.97</v>
+        <v>766972.97</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>764822.97</v>
+        <v>766972.97</v>
       </c>
     </row>
     <row r="19">
@@ -1266,13 +1266,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>764822.97</v>
+        <v>766972.97</v>
       </c>
       <c r="E19" t="n">
         <v>30000</v>
       </c>
       <c r="F19" t="n">
-        <v>794822.97</v>
+        <v>796972.97</v>
       </c>
     </row>
     <row r="20">
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>794822.97</v>
+        <v>796972.97</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>794822.97</v>
+        <v>796972.97</v>
       </c>
     </row>
     <row r="21">
@@ -1318,13 +1318,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>794822.97</v>
+        <v>796972.97</v>
       </c>
       <c r="E21" t="n">
         <v>-114792.19</v>
       </c>
       <c r="F21" t="n">
-        <v>680030.78</v>
+        <v>682180.78</v>
       </c>
     </row>
     <row r="22">
@@ -1344,13 +1344,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>680030.78</v>
+        <v>682180.78</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>680030.78</v>
+        <v>682180.78</v>
       </c>
     </row>
     <row r="23">
@@ -1370,13 +1370,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>680030.78</v>
+        <v>682180.78</v>
       </c>
       <c r="E23" t="n">
         <v>369.22</v>
       </c>
       <c r="F23" t="n">
-        <v>680400</v>
+        <v>682550</v>
       </c>
     </row>
   </sheetData>
